--- a/model_info/gemini_realset.xlsx
+++ b/model_info/gemini_realset.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="9.9" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.2700719993472824</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.09343850875788193</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.18376033968927596</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.6606128246753247</v>
+        <v>0.34458603896103895</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         <v>0.8106535524993804</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.5945982430689878</v>
+        <v>0.27640635074145714</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>0.7536047165172917</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.1348692525566187</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.5196759259259259</v>
+        <v>0.03935185185185186</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.3201288845762984</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.34834828481155494</v>
+        <v>0.07278266756939741</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.07621241953096713</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.4668760778516876</v>
+        <v>0.028258191672825828</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.18952747084116808</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.042782738095238096</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.1589718787820826</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.5444444444444444</v>
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
